--- a/player.xlsx
+++ b/player.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9ad26968bd40fff/바탕 화면/내전 팀짜기/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_045466BC9154C984F72A0E2BF8800DD8633030B9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{321E41A9-DFE0-46EF-ACC4-BC4767622100}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{0F1C30E8-7A8B-4BCA-A063-D5EC52976833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6CD4AB9-2C39-4C5D-B809-21B4FF28B35E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="29580" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33285" yWindow="1785" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -163,9 +176,6 @@
     <t>예이범절</t>
   </si>
   <si>
-    <t>*현</t>
-  </si>
-  <si>
     <t>임동규</t>
   </si>
   <si>
@@ -173,6 +183,10 @@
   </si>
   <si>
     <t>이름</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>소현</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -203,7 +217,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,14 +238,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF4B084"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor rgb="FFF4B084"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF548235"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor rgb="FF548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor rgb="FF548235"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor rgb="FFF4B084"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -339,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -359,31 +397,43 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -607,12 +657,12 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -633,496 +683,519 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" ht="14.25">
       <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="14">
         <v>3.7</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="18">
         <v>4.0999999999999996</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>3.65</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>3.8</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>3.5</v>
       </c>
-      <c r="H2" s="9">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="H2" s="8">
+        <f>AVERAGE(C2:G2)</f>
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8">
+      <c r="C3" s="7"/>
+      <c r="D3" s="14">
         <v>3.8</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="18">
         <v>4.2</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <v>3.7</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="9">
+      <c r="G3" s="7"/>
+      <c r="H3" s="8">
+        <f t="shared" ref="H3:H23" si="0">AVERAGE(C3:G3)</f>
         <v>3.9</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="14.25">
       <c r="A4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="14">
         <v>3.5</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="18">
         <v>3.7</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="9">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="8">
+        <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" ht="14.25">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8">
+      <c r="C5" s="7"/>
+      <c r="D5" s="18">
         <v>4</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8">
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="14">
         <v>3.5</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
+        <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" ht="14.25">
       <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8">
+      <c r="C6" s="7"/>
+      <c r="D6" s="14">
         <v>3.5</v>
       </c>
       <c r="E6" s="7">
         <v>3.2</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>3.4</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="18">
         <v>3.6</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
+        <f t="shared" si="0"/>
         <v>3.4249999999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" ht="14.25">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="18">
         <v>3.45</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="14">
         <v>3.4</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>3.4</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9">
-        <v>3.4166666700000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8">
+        <f t="shared" si="0"/>
+        <v>3.4166666666666665</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.25">
       <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>3.35</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="14">
         <v>3.5</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8">
+      <c r="E8" s="7"/>
+      <c r="F8" s="18">
         <v>3.7</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="7">
         <v>3.15</v>
       </c>
-      <c r="H8" s="9">
-        <v>3.4249999999999998</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8" s="8">
+        <f t="shared" si="0"/>
+        <v>3.4250000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.25">
       <c r="A9" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="14">
         <v>3.5</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>3.35</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="18">
         <v>3.6</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>3.3</v>
       </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9">
+      <c r="G9" s="7"/>
+      <c r="H9" s="8">
+        <f t="shared" si="0"/>
         <v>3.4375</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" ht="14.25">
       <c r="A10" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>3.2</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="16">
         <v>3.55</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>3.1</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="14">
         <v>3.4</v>
       </c>
-      <c r="G10" s="8"/>
-      <c r="H10" s="9">
+      <c r="G10" s="7"/>
+      <c r="H10" s="8">
+        <f t="shared" si="0"/>
         <v>3.3125</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" ht="14.25">
       <c r="A11" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>3.15</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="14">
         <v>3.4</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="16">
         <v>3.4</v>
       </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="9">
-        <v>3.31666667</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="8">
+        <f t="shared" si="0"/>
+        <v>3.3166666666666664</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.25">
       <c r="A12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>3.1</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="17">
         <v>3.6</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>3.1</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="10">
+      <c r="F12" s="7"/>
+      <c r="G12" s="15">
         <v>3.5</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="8">
+        <f t="shared" si="0"/>
         <v>3.3250000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="14.25">
       <c r="A13" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="14">
         <v>3.3</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>3.1</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="17">
         <v>3.7</v>
       </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="9">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="8">
+        <f t="shared" si="0"/>
+        <v>3.3666666666666671</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.25">
       <c r="A14" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8">
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="14">
         <v>3.3</v>
       </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7">
+      <c r="F14" s="7"/>
+      <c r="G14" s="17">
         <v>3.8</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="8">
+        <f t="shared" si="0"/>
         <v>3.55</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="14.25">
       <c r="A15" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="18">
         <v>3.35</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8">
+      <c r="D15" s="7"/>
+      <c r="E15" s="14">
         <v>3.3</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="9">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="8">
+        <f t="shared" si="0"/>
         <v>3.3250000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" ht="14.25">
       <c r="A16" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="16">
         <v>3.4</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>3.1</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8">
+      <c r="E16" s="7"/>
+      <c r="F16" s="14">
         <v>3.2</v>
       </c>
-      <c r="G16" s="8"/>
-      <c r="H16" s="9">
-        <v>3.2333333299999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="G16" s="7"/>
+      <c r="H16" s="8">
+        <f t="shared" si="0"/>
+        <v>3.2333333333333329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="14.25">
       <c r="A17" s="5" t="s">
         <v>36</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>3</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="18">
         <v>3.5</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>3.2</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="13">
         <v>3.35</v>
       </c>
-      <c r="G17" s="8">
+      <c r="G17" s="7">
         <v>3.1</v>
       </c>
-      <c r="H17" s="9">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="H17" s="8">
+        <f t="shared" si="0"/>
+        <v>3.2299999999999995</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="14.25">
       <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>3.25</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="14">
         <v>3.3</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>3</v>
       </c>
-      <c r="F18" s="8">
+      <c r="F18" s="7">
         <v>3.2</v>
       </c>
-      <c r="G18" s="8">
+      <c r="G18" s="18">
         <v>3.5</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="8">
+        <f t="shared" si="0"/>
         <v>3.25</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:8" ht="14.25">
+      <c r="A19" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="14">
         <v>3.2</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8">
+      <c r="D19" s="7"/>
+      <c r="E19" s="18">
         <v>3.2</v>
       </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="9">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="8">
+        <f t="shared" si="0"/>
         <v>3.2</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" ht="14.25">
       <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8">
+      <c r="D20" s="7"/>
+      <c r="E20" s="7">
         <v>2.95</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="17">
         <v>3.3</v>
       </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="9">
-        <v>3.0833333299999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="G20" s="7"/>
+      <c r="H20" s="8">
+        <f t="shared" si="0"/>
+        <v>3.0833333333333335</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="14.25">
       <c r="A21" s="5" t="s">
         <v>44</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="10">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="16">
         <v>3.5</v>
       </c>
-      <c r="G21" s="8">
-        <v>3</v>
-      </c>
-      <c r="H21" s="9">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="G21" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="0"/>
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="14.25">
       <c r="A22" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="14">
+        <v>2.7</v>
+      </c>
+      <c r="F22" s="7"/>
+      <c r="G22" s="18">
+        <v>2.8</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="0"/>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="14.25">
+      <c r="A23" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8">
+      <c r="B23" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="19">
         <v>3</v>
       </c>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8">
-        <v>3</v>
-      </c>
-      <c r="H22" s="9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14">
-        <v>3</v>
-      </c>
-      <c r="H23" s="15">
+      <c r="H23" s="8">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/player.xlsx
+++ b/player.xlsx
@@ -451,6 +451,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/player.xlsx
+++ b/player.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9ad26968bd40fff/바탕 화면/내전 팀짜기/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ST-USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{0F1C30E8-7A8B-4BCA-A063-D5EC52976833}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6CD4AB9-2C39-4C5D-B809-21B4FF28B35E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36ACD2-E126-4E69-AB94-995E851D2A58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33285" yWindow="1785" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32805" yWindow="2775" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -217,7 +212,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -234,12 +229,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor rgb="FFF4B084"/>
       </patternFill>
     </fill>
     <fill>
@@ -377,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -430,10 +419,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -694,10 +680,10 @@
       <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>3.7</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D2" s="17">
         <v>4.0999999999999996</v>
       </c>
       <c r="E2" s="7">
@@ -722,10 +708,10 @@
         <v>10</v>
       </c>
       <c r="C3" s="7"/>
-      <c r="D3" s="14">
+      <c r="D3" s="13">
         <v>3.8</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="17">
         <v>4.2</v>
       </c>
       <c r="F3" s="7">
@@ -744,10 +730,10 @@
       <c r="B4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <v>3.5</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <v>3.7</v>
       </c>
       <c r="E4" s="7"/>
@@ -766,12 +752,12 @@
         <v>14</v>
       </c>
       <c r="C5" s="7"/>
-      <c r="D5" s="18">
+      <c r="D5" s="17">
         <v>4</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>3.5</v>
       </c>
       <c r="H5" s="8">
@@ -787,7 +773,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="7"/>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <v>3.5</v>
       </c>
       <c r="E6" s="7">
@@ -796,7 +782,7 @@
       <c r="F6" s="7">
         <v>3.4</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <v>3.6</v>
       </c>
       <c r="H6" s="8">
@@ -811,10 +797,10 @@
       <c r="B7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <v>3.45</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <v>3.4</v>
       </c>
       <c r="E7" s="7">
@@ -837,11 +823,11 @@
       <c r="C8" s="7">
         <v>3.35</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <v>3.5</v>
       </c>
       <c r="E8" s="7"/>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>3.7</v>
       </c>
       <c r="G8" s="7">
@@ -859,13 +845,13 @@
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="13">
         <v>3.5</v>
       </c>
       <c r="D9" s="7">
         <v>3.35</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>3.6</v>
       </c>
       <c r="F9" s="7">
@@ -887,13 +873,13 @@
       <c r="C10" s="7">
         <v>3.2</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <v>3.55</v>
       </c>
       <c r="E10" s="7">
         <v>3.1</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <v>3.4</v>
       </c>
       <c r="G10" s="7"/>
@@ -912,10 +898,10 @@
       <c r="C11" s="7">
         <v>3.15</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <v>3.4</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="15">
         <v>3.4</v>
       </c>
       <c r="F11" s="7"/>
@@ -935,14 +921,14 @@
       <c r="C12" s="7">
         <v>3.1</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <v>3.6</v>
       </c>
       <c r="E12" s="7">
         <v>3.1</v>
       </c>
       <c r="F12" s="7"/>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <v>3.5</v>
       </c>
       <c r="H12" s="8">
@@ -957,13 +943,13 @@
       <c r="B13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <v>3.3</v>
       </c>
       <c r="D13" s="7">
         <v>3.1</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>3.7</v>
       </c>
       <c r="F13" s="7"/>
@@ -982,11 +968,11 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>3.3</v>
       </c>
       <c r="F14" s="7"/>
-      <c r="G14" s="17">
+      <c r="G14" s="16">
         <v>3.8</v>
       </c>
       <c r="H14" s="8">
@@ -1001,11 +987,11 @@
       <c r="B15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>3.35</v>
       </c>
       <c r="D15" s="7"/>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>3.3</v>
       </c>
       <c r="F15" s="7"/>
@@ -1022,14 +1008,14 @@
       <c r="B16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="15">
         <v>3.4</v>
       </c>
       <c r="D16" s="7">
         <v>3.1</v>
       </c>
       <c r="E16" s="7"/>
-      <c r="F16" s="14">
+      <c r="F16" s="13">
         <v>3.2</v>
       </c>
       <c r="G16" s="7"/>
@@ -1048,13 +1034,13 @@
       <c r="C17" s="7">
         <v>3</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="14">
         <v>3.5</v>
       </c>
       <c r="E17" s="7">
         <v>3.2</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="16">
         <v>3.35</v>
       </c>
       <c r="G17" s="7">
@@ -1075,7 +1061,7 @@
       <c r="C18" s="7">
         <v>3.25</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="13">
         <v>3.3</v>
       </c>
       <c r="E18" s="7">
@@ -1084,7 +1070,7 @@
       <c r="F18" s="7">
         <v>3.2</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <v>3.5</v>
       </c>
       <c r="H18" s="8">
@@ -1099,11 +1085,11 @@
       <c r="B19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C19" s="13">
         <v>3.2</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>3.2</v>
       </c>
       <c r="F19" s="7"/>
@@ -1120,14 +1106,14 @@
       <c r="B20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <v>3</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7">
         <v>2.95</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="16">
         <v>3.3</v>
       </c>
       <c r="G20" s="7"/>
@@ -1146,10 +1132,10 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="16">
+      <c r="F21" s="15">
         <v>3.5</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="13">
         <v>2.8</v>
       </c>
       <c r="H21" s="8">
@@ -1166,11 +1152,11 @@
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="14">
+      <c r="E22" s="13">
         <v>2.7</v>
       </c>
       <c r="F22" s="7"/>
-      <c r="G22" s="18">
+      <c r="G22" s="17">
         <v>2.8</v>
       </c>
       <c r="H22" s="8">
@@ -1189,7 +1175,7 @@
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
-      <c r="G23" s="19">
+      <c r="G23" s="18">
         <v>3</v>
       </c>
       <c r="H23" s="8">

--- a/player.xlsx
+++ b/player.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ST-USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ST-USER\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36ACD2-E126-4E69-AB94-995E851D2A58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E33CE94-8AB4-4E92-A2E8-7312A7AB347A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32805" yWindow="2775" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4740" yWindow="2475" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -736,12 +736,14 @@
       <c r="D4" s="17">
         <v>3.7</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="7">
+        <v>3.5</v>
+      </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="8">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>3.5666666666666664</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.25">
@@ -1014,14 +1016,16 @@
       <c r="D16" s="7">
         <v>3.1</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="7">
+        <v>3.2</v>
+      </c>
       <c r="F16" s="13">
         <v>3.2</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="8">
         <f t="shared" si="0"/>
-        <v>3.2333333333333329</v>
+        <v>3.2249999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="14.25">
@@ -1093,10 +1097,12 @@
         <v>3.2</v>
       </c>
       <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="G19" s="7">
+        <v>2.8</v>
+      </c>
       <c r="H19" s="8">
         <f t="shared" si="0"/>
-        <v>3.2</v>
+        <v>3.0666666666666664</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="14.25">
